--- a/data/XRD/2 Round/Mo_125Se_200Sb_35Se.xlsx
+++ b/data/XRD/2 Round/Mo_125Se_200Sb_35Se.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fbdd27f2520478cf/Ambiente de Trabalho/TESE/Data_Analysis/data/XRD/2 Round/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EF16F0B3-8442-4874-B5AA-8A5A8F45AD51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{EF16F0B3-8442-4874-B5AA-8A5A8F45AD51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E47CF7D1-A45B-49CB-97D3-BD9160552494}"/>
   <bookViews>
-    <workbookView xWindow="2412" yWindow="948" windowWidth="17280" windowHeight="8880" xr2:uid="{38A11229-5A15-469D-8F81-B9213AB719A7}"/>
+    <workbookView xWindow="1920" yWindow="1920" windowWidth="17280" windowHeight="8880" xr2:uid="{38A11229-5A15-469D-8F81-B9213AB719A7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="272">
   <si>
     <t>No.</t>
   </si>
@@ -230,30 +230,6 @@
     <t>0,174166</t>
   </si>
   <si>
-    <t>25,93(7)</t>
-  </si>
-  <si>
-    <t>3,1(2)</t>
-  </si>
-  <si>
-    <t>759,02</t>
-  </si>
-  <si>
-    <t>778,01</t>
-  </si>
-  <si>
-    <t>3,43352</t>
-  </si>
-  <si>
-    <t>161(6)</t>
-  </si>
-  <si>
-    <t>1,56</t>
-  </si>
-  <si>
-    <t>4,702619</t>
-  </si>
-  <si>
     <t>27,53(6)</t>
   </si>
   <si>
@@ -425,30 +401,6 @@
     <t>0,122881</t>
   </si>
   <si>
-    <t>34,266(1)</t>
-  </si>
-  <si>
-    <t>0,385(3)</t>
-  </si>
-  <si>
-    <t>1099,38</t>
-  </si>
-  <si>
-    <t>732,77</t>
-  </si>
-  <si>
-    <t>2,61484</t>
-  </si>
-  <si>
-    <t>2390(22)</t>
-  </si>
-  <si>
-    <t>23,02</t>
-  </si>
-  <si>
-    <t>0,460038</t>
-  </si>
-  <si>
     <t>35,635(2)</t>
   </si>
   <si>
@@ -779,9 +731,6 @@
     <t>276(9)</t>
   </si>
   <si>
-    <t>01-089-5156; 00-015-0861; 00-029-0914</t>
-  </si>
-  <si>
     <t>2,66</t>
   </si>
   <si>
@@ -834,6 +783,78 @@
   </si>
   <si>
     <t>0,967501</t>
+  </si>
+  <si>
+    <t>34,174(5)</t>
+  </si>
+  <si>
+    <t>0,19(1)</t>
+  </si>
+  <si>
+    <t>583,27</t>
+  </si>
+  <si>
+    <t>762,86</t>
+  </si>
+  <si>
+    <t>2,62164</t>
+  </si>
+  <si>
+    <t>1950(63)</t>
+  </si>
+  <si>
+    <t>18,79</t>
+  </si>
+  <si>
+    <t>0,299064</t>
+  </si>
+  <si>
+    <t>34,33(2)</t>
+  </si>
+  <si>
+    <t>0,24(4)</t>
+  </si>
+  <si>
+    <t>395,38</t>
+  </si>
+  <si>
+    <t>772,81</t>
+  </si>
+  <si>
+    <t>2,61024</t>
+  </si>
+  <si>
+    <t>1092(113)</t>
+  </si>
+  <si>
+    <t>10,52</t>
+  </si>
+  <si>
+    <t>0,362062</t>
+  </si>
+  <si>
+    <t>34,39(4)</t>
+  </si>
+  <si>
+    <t>0,25(9)</t>
+  </si>
+  <si>
+    <t>175,35</t>
+  </si>
+  <si>
+    <t>774,86</t>
+  </si>
+  <si>
+    <t>2,60568</t>
+  </si>
+  <si>
+    <t>503(96)</t>
+  </si>
+  <si>
+    <t>0,348781</t>
+  </si>
+  <si>
+    <t>01-089-5156; 00-015-0861</t>
   </si>
 </sst>
 </file>
@@ -1205,7 +1226,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C326E01-0540-4960-B2A0-1D05EF906DF6}">
-  <dimension ref="A1:W30"/>
+  <dimension ref="A1:W31"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.3">
@@ -1541,10 +1562,13 @@
         <v>32</v>
       </c>
       <c r="R6" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="S6" t="s">
+        <v>69</v>
       </c>
       <c r="T6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="U6" t="s">
         <v>35</v>
@@ -1553,7 +1577,7 @@
         <v>36</v>
       </c>
       <c r="W6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.3">
@@ -1561,10 +1585,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D7" t="s">
         <v>25</v>
@@ -1576,19 +1600,19 @@
         <v>26</v>
       </c>
       <c r="L7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="M7" t="s">
         <v>28</v>
       </c>
       <c r="N7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="O7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="P7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Q7" t="s">
         <v>32</v>
@@ -1597,7 +1621,7 @@
         <v>1</v>
       </c>
       <c r="S7" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="T7" t="s">
         <v>78</v>
@@ -1653,7 +1677,7 @@
         <v>1</v>
       </c>
       <c r="S8" t="s">
-        <v>77</v>
+        <v>44</v>
       </c>
       <c r="T8" t="s">
         <v>86</v>
@@ -1709,7 +1733,7 @@
         <v>1</v>
       </c>
       <c r="S9" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="T9" t="s">
         <v>94</v>
@@ -1762,10 +1786,7 @@
         <v>32</v>
       </c>
       <c r="R10" t="b">
-        <v>1</v>
-      </c>
-      <c r="S10" t="s">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="T10" t="s">
         <v>102</v>
@@ -1821,7 +1842,7 @@
         <v>1</v>
       </c>
       <c r="S11" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="T11" t="s">
         <v>110</v>
@@ -1897,10 +1918,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>120</v>
+        <v>248</v>
       </c>
       <c r="C13" t="s">
-        <v>121</v>
+        <v>249</v>
       </c>
       <c r="D13" t="s">
         <v>25</v>
@@ -1912,19 +1933,19 @@
         <v>26</v>
       </c>
       <c r="L13" t="s">
-        <v>122</v>
+        <v>250</v>
       </c>
       <c r="M13" t="s">
         <v>28</v>
       </c>
       <c r="N13" t="s">
-        <v>123</v>
+        <v>251</v>
       </c>
       <c r="O13" t="s">
-        <v>124</v>
+        <v>252</v>
       </c>
       <c r="P13" t="s">
-        <v>125</v>
+        <v>253</v>
       </c>
       <c r="Q13" t="s">
         <v>32</v>
@@ -1933,10 +1954,10 @@
         <v>1</v>
       </c>
       <c r="S13" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="T13" t="s">
-        <v>126</v>
+        <v>254</v>
       </c>
       <c r="U13" t="s">
         <v>35</v>
@@ -1945,7 +1966,7 @@
         <v>36</v>
       </c>
       <c r="W13" t="s">
-        <v>127</v>
+        <v>255</v>
       </c>
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.3">
@@ -1953,10 +1974,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>128</v>
+        <v>256</v>
       </c>
       <c r="C14" t="s">
-        <v>129</v>
+        <v>257</v>
       </c>
       <c r="D14" t="s">
         <v>25</v>
@@ -1968,19 +1989,19 @@
         <v>26</v>
       </c>
       <c r="L14" t="s">
-        <v>130</v>
+        <v>258</v>
       </c>
       <c r="M14" t="s">
         <v>28</v>
       </c>
       <c r="N14" t="s">
-        <v>131</v>
+        <v>259</v>
       </c>
       <c r="O14" t="s">
-        <v>132</v>
+        <v>260</v>
       </c>
       <c r="P14" t="s">
-        <v>133</v>
+        <v>261</v>
       </c>
       <c r="Q14" t="s">
         <v>32</v>
@@ -1989,10 +2010,10 @@
         <v>1</v>
       </c>
       <c r="S14" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="T14" t="s">
-        <v>134</v>
+        <v>262</v>
       </c>
       <c r="U14" t="s">
         <v>35</v>
@@ -2001,7 +2022,7 @@
         <v>36</v>
       </c>
       <c r="W14" t="s">
-        <v>135</v>
+        <v>263</v>
       </c>
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.3">
@@ -2009,10 +2030,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>136</v>
+        <v>264</v>
       </c>
       <c r="C15" t="s">
-        <v>137</v>
+        <v>265</v>
       </c>
       <c r="D15" t="s">
         <v>25</v>
@@ -2024,19 +2045,19 @@
         <v>26</v>
       </c>
       <c r="L15" t="s">
-        <v>138</v>
+        <v>266</v>
       </c>
       <c r="M15" t="s">
         <v>28</v>
       </c>
       <c r="N15" t="s">
-        <v>139</v>
+        <v>267</v>
       </c>
       <c r="O15" t="s">
-        <v>140</v>
+        <v>268</v>
       </c>
       <c r="P15" t="s">
-        <v>141</v>
+        <v>269</v>
       </c>
       <c r="Q15" t="s">
         <v>32</v>
@@ -2045,10 +2066,10 @@
         <v>1</v>
       </c>
       <c r="S15" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="T15" t="s">
-        <v>142</v>
+        <v>53</v>
       </c>
       <c r="U15" t="s">
         <v>35</v>
@@ -2057,7 +2078,7 @@
         <v>36</v>
       </c>
       <c r="W15" t="s">
-        <v>143</v>
+        <v>270</v>
       </c>
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.3">
@@ -2065,10 +2086,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="C16" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="D16" t="s">
         <v>25</v>
@@ -2080,28 +2101,31 @@
         <v>26</v>
       </c>
       <c r="L16" t="s">
-        <v>146</v>
+        <v>122</v>
       </c>
       <c r="M16" t="s">
         <v>28</v>
       </c>
       <c r="N16" t="s">
-        <v>147</v>
+        <v>123</v>
       </c>
       <c r="O16" t="s">
-        <v>148</v>
+        <v>124</v>
       </c>
       <c r="P16" t="s">
-        <v>149</v>
+        <v>125</v>
       </c>
       <c r="Q16" t="s">
         <v>32</v>
       </c>
       <c r="R16" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="S16" t="s">
+        <v>44</v>
       </c>
       <c r="T16" t="s">
-        <v>150</v>
+        <v>126</v>
       </c>
       <c r="U16" t="s">
         <v>35</v>
@@ -2110,7 +2134,7 @@
         <v>36</v>
       </c>
       <c r="W16" t="s">
-        <v>151</v>
+        <v>127</v>
       </c>
     </row>
     <row r="17" spans="1:23" x14ac:dyDescent="0.3">
@@ -2118,10 +2142,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>152</v>
+        <v>128</v>
       </c>
       <c r="C17" t="s">
-        <v>153</v>
+        <v>129</v>
       </c>
       <c r="D17" t="s">
         <v>25</v>
@@ -2133,31 +2157,28 @@
         <v>26</v>
       </c>
       <c r="L17" t="s">
-        <v>154</v>
+        <v>130</v>
       </c>
       <c r="M17" t="s">
         <v>28</v>
       </c>
       <c r="N17" t="s">
-        <v>155</v>
+        <v>131</v>
       </c>
       <c r="O17" t="s">
-        <v>156</v>
+        <v>132</v>
       </c>
       <c r="P17" t="s">
-        <v>157</v>
+        <v>133</v>
       </c>
       <c r="Q17" t="s">
         <v>32</v>
       </c>
       <c r="R17" t="b">
-        <v>1</v>
-      </c>
-      <c r="S17" t="s">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="T17" t="s">
-        <v>158</v>
+        <v>134</v>
       </c>
       <c r="U17" t="s">
         <v>35</v>
@@ -2166,7 +2187,7 @@
         <v>36</v>
       </c>
       <c r="W17" t="s">
-        <v>159</v>
+        <v>135</v>
       </c>
     </row>
     <row r="18" spans="1:23" x14ac:dyDescent="0.3">
@@ -2174,10 +2195,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>160</v>
+        <v>136</v>
       </c>
       <c r="C18" t="s">
-        <v>161</v>
+        <v>137</v>
       </c>
       <c r="D18" t="s">
         <v>25</v>
@@ -2189,19 +2210,19 @@
         <v>26</v>
       </c>
       <c r="L18" t="s">
-        <v>162</v>
+        <v>138</v>
       </c>
       <c r="M18" t="s">
         <v>28</v>
       </c>
       <c r="N18" t="s">
-        <v>163</v>
+        <v>139</v>
       </c>
       <c r="O18" t="s">
-        <v>164</v>
+        <v>140</v>
       </c>
       <c r="P18" t="s">
-        <v>165</v>
+        <v>141</v>
       </c>
       <c r="Q18" t="s">
         <v>32</v>
@@ -2210,10 +2231,10 @@
         <v>1</v>
       </c>
       <c r="S18" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="T18" t="s">
-        <v>166</v>
+        <v>142</v>
       </c>
       <c r="U18" t="s">
         <v>35</v>
@@ -2222,7 +2243,7 @@
         <v>36</v>
       </c>
       <c r="W18" t="s">
-        <v>167</v>
+        <v>143</v>
       </c>
     </row>
     <row r="19" spans="1:23" x14ac:dyDescent="0.3">
@@ -2230,10 +2251,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>168</v>
+        <v>144</v>
       </c>
       <c r="C19" t="s">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="D19" t="s">
         <v>25</v>
@@ -2245,19 +2266,19 @@
         <v>26</v>
       </c>
       <c r="L19" t="s">
-        <v>170</v>
+        <v>146</v>
       </c>
       <c r="M19" t="s">
         <v>28</v>
       </c>
       <c r="N19" t="s">
-        <v>171</v>
+        <v>147</v>
       </c>
       <c r="O19" t="s">
-        <v>172</v>
+        <v>148</v>
       </c>
       <c r="P19" t="s">
-        <v>173</v>
+        <v>149</v>
       </c>
       <c r="Q19" t="s">
         <v>32</v>
@@ -2266,10 +2287,10 @@
         <v>1</v>
       </c>
       <c r="S19" t="s">
-        <v>174</v>
+        <v>44</v>
       </c>
       <c r="T19" t="s">
-        <v>175</v>
+        <v>150</v>
       </c>
       <c r="U19" t="s">
         <v>35</v>
@@ -2278,7 +2299,7 @@
         <v>36</v>
       </c>
       <c r="W19" t="s">
-        <v>176</v>
+        <v>151</v>
       </c>
     </row>
     <row r="20" spans="1:23" x14ac:dyDescent="0.3">
@@ -2286,10 +2307,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>177</v>
+        <v>152</v>
       </c>
       <c r="C20" t="s">
-        <v>178</v>
+        <v>153</v>
       </c>
       <c r="D20" t="s">
         <v>25</v>
@@ -2301,19 +2322,19 @@
         <v>26</v>
       </c>
       <c r="L20" t="s">
-        <v>179</v>
+        <v>154</v>
       </c>
       <c r="M20" t="s">
         <v>28</v>
       </c>
       <c r="N20" t="s">
-        <v>180</v>
+        <v>155</v>
       </c>
       <c r="O20" t="s">
-        <v>181</v>
+        <v>156</v>
       </c>
       <c r="P20" t="s">
-        <v>182</v>
+        <v>157</v>
       </c>
       <c r="Q20" t="s">
         <v>32</v>
@@ -2322,10 +2343,10 @@
         <v>1</v>
       </c>
       <c r="S20" t="s">
-        <v>174</v>
+        <v>158</v>
       </c>
       <c r="T20" t="s">
-        <v>183</v>
+        <v>159</v>
       </c>
       <c r="U20" t="s">
         <v>35</v>
@@ -2334,7 +2355,7 @@
         <v>36</v>
       </c>
       <c r="W20" t="s">
-        <v>184</v>
+        <v>160</v>
       </c>
     </row>
     <row r="21" spans="1:23" x14ac:dyDescent="0.3">
@@ -2342,10 +2363,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>185</v>
+        <v>161</v>
       </c>
       <c r="C21" t="s">
-        <v>186</v>
+        <v>162</v>
       </c>
       <c r="D21" t="s">
         <v>25</v>
@@ -2357,19 +2378,19 @@
         <v>26</v>
       </c>
       <c r="L21" t="s">
-        <v>187</v>
+        <v>163</v>
       </c>
       <c r="M21" t="s">
         <v>28</v>
       </c>
       <c r="N21" t="s">
-        <v>188</v>
+        <v>164</v>
       </c>
       <c r="O21" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="P21" t="s">
-        <v>190</v>
+        <v>166</v>
       </c>
       <c r="Q21" t="s">
         <v>32</v>
@@ -2378,10 +2399,10 @@
         <v>1</v>
       </c>
       <c r="S21" t="s">
-        <v>44</v>
+        <v>158</v>
       </c>
       <c r="T21" t="s">
-        <v>191</v>
+        <v>167</v>
       </c>
       <c r="U21" t="s">
         <v>35</v>
@@ -2390,7 +2411,7 @@
         <v>36</v>
       </c>
       <c r="W21" t="s">
-        <v>192</v>
+        <v>168</v>
       </c>
     </row>
     <row r="22" spans="1:23" x14ac:dyDescent="0.3">
@@ -2398,10 +2419,10 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
       <c r="C22" t="s">
-        <v>194</v>
+        <v>170</v>
       </c>
       <c r="D22" t="s">
         <v>25</v>
@@ -2413,19 +2434,19 @@
         <v>26</v>
       </c>
       <c r="L22" t="s">
-        <v>195</v>
+        <v>171</v>
       </c>
       <c r="M22" t="s">
         <v>28</v>
       </c>
       <c r="N22" t="s">
-        <v>196</v>
+        <v>172</v>
       </c>
       <c r="O22" t="s">
-        <v>197</v>
+        <v>173</v>
       </c>
       <c r="P22" t="s">
-        <v>198</v>
+        <v>174</v>
       </c>
       <c r="Q22" t="s">
         <v>32</v>
@@ -2437,7 +2458,7 @@
         <v>44</v>
       </c>
       <c r="T22" t="s">
-        <v>199</v>
+        <v>175</v>
       </c>
       <c r="U22" t="s">
         <v>35</v>
@@ -2446,7 +2467,7 @@
         <v>36</v>
       </c>
       <c r="W22" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
     </row>
     <row r="23" spans="1:23" x14ac:dyDescent="0.3">
@@ -2454,10 +2475,10 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>201</v>
+        <v>177</v>
       </c>
       <c r="C23" t="s">
-        <v>202</v>
+        <v>178</v>
       </c>
       <c r="D23" t="s">
         <v>25</v>
@@ -2469,19 +2490,19 @@
         <v>26</v>
       </c>
       <c r="L23" t="s">
-        <v>203</v>
+        <v>179</v>
       </c>
       <c r="M23" t="s">
         <v>28</v>
       </c>
       <c r="N23" t="s">
-        <v>204</v>
+        <v>180</v>
       </c>
       <c r="O23" t="s">
-        <v>205</v>
+        <v>181</v>
       </c>
       <c r="P23" t="s">
-        <v>206</v>
+        <v>182</v>
       </c>
       <c r="Q23" t="s">
         <v>32</v>
@@ -2490,10 +2511,10 @@
         <v>1</v>
       </c>
       <c r="S23" t="s">
-        <v>77</v>
+        <v>44</v>
       </c>
       <c r="T23" t="s">
-        <v>207</v>
+        <v>183</v>
       </c>
       <c r="U23" t="s">
         <v>35</v>
@@ -2502,7 +2523,7 @@
         <v>36</v>
       </c>
       <c r="W23" t="s">
-        <v>208</v>
+        <v>184</v>
       </c>
     </row>
     <row r="24" spans="1:23" x14ac:dyDescent="0.3">
@@ -2510,10 +2531,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>209</v>
+        <v>185</v>
       </c>
       <c r="C24" t="s">
-        <v>210</v>
+        <v>186</v>
       </c>
       <c r="D24" t="s">
         <v>25</v>
@@ -2525,19 +2546,19 @@
         <v>26</v>
       </c>
       <c r="L24" t="s">
-        <v>211</v>
+        <v>187</v>
       </c>
       <c r="M24" t="s">
         <v>28</v>
       </c>
       <c r="N24" t="s">
-        <v>212</v>
+        <v>188</v>
       </c>
       <c r="O24" t="s">
-        <v>213</v>
+        <v>189</v>
       </c>
       <c r="P24" t="s">
-        <v>214</v>
+        <v>190</v>
       </c>
       <c r="Q24" t="s">
         <v>32</v>
@@ -2546,10 +2567,10 @@
         <v>1</v>
       </c>
       <c r="S24" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="T24" t="s">
-        <v>215</v>
+        <v>191</v>
       </c>
       <c r="U24" t="s">
         <v>35</v>
@@ -2558,7 +2579,7 @@
         <v>36</v>
       </c>
       <c r="W24" t="s">
-        <v>216</v>
+        <v>192</v>
       </c>
     </row>
     <row r="25" spans="1:23" x14ac:dyDescent="0.3">
@@ -2566,10 +2587,10 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>217</v>
+        <v>193</v>
       </c>
       <c r="C25" t="s">
-        <v>218</v>
+        <v>194</v>
       </c>
       <c r="D25" t="s">
         <v>25</v>
@@ -2581,19 +2602,19 @@
         <v>26</v>
       </c>
       <c r="L25" t="s">
-        <v>219</v>
+        <v>195</v>
       </c>
       <c r="M25" t="s">
         <v>28</v>
       </c>
       <c r="N25" t="s">
-        <v>220</v>
+        <v>196</v>
       </c>
       <c r="O25" t="s">
-        <v>221</v>
+        <v>197</v>
       </c>
       <c r="P25" t="s">
-        <v>222</v>
+        <v>198</v>
       </c>
       <c r="Q25" t="s">
         <v>32</v>
@@ -2605,7 +2626,7 @@
         <v>44</v>
       </c>
       <c r="T25" t="s">
-        <v>223</v>
+        <v>199</v>
       </c>
       <c r="U25" t="s">
         <v>35</v>
@@ -2614,7 +2635,7 @@
         <v>36</v>
       </c>
       <c r="W25" t="s">
-        <v>224</v>
+        <v>200</v>
       </c>
     </row>
     <row r="26" spans="1:23" x14ac:dyDescent="0.3">
@@ -2622,10 +2643,10 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>225</v>
+        <v>201</v>
       </c>
       <c r="C26" t="s">
-        <v>226</v>
+        <v>202</v>
       </c>
       <c r="D26" t="s">
         <v>25</v>
@@ -2637,19 +2658,19 @@
         <v>26</v>
       </c>
       <c r="L26" t="s">
-        <v>227</v>
+        <v>203</v>
       </c>
       <c r="M26" t="s">
         <v>28</v>
       </c>
       <c r="N26" t="s">
-        <v>228</v>
+        <v>204</v>
       </c>
       <c r="O26" t="s">
-        <v>229</v>
+        <v>205</v>
       </c>
       <c r="P26" t="s">
-        <v>230</v>
+        <v>206</v>
       </c>
       <c r="Q26" t="s">
         <v>32</v>
@@ -2661,7 +2682,7 @@
         <v>44</v>
       </c>
       <c r="T26" t="s">
-        <v>231</v>
+        <v>207</v>
       </c>
       <c r="U26" t="s">
         <v>35</v>
@@ -2670,7 +2691,7 @@
         <v>36</v>
       </c>
       <c r="W26" t="s">
-        <v>232</v>
+        <v>208</v>
       </c>
     </row>
     <row r="27" spans="1:23" x14ac:dyDescent="0.3">
@@ -2678,10 +2699,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>233</v>
+        <v>209</v>
       </c>
       <c r="C27" t="s">
-        <v>186</v>
+        <v>210</v>
       </c>
       <c r="D27" t="s">
         <v>25</v>
@@ -2693,19 +2714,19 @@
         <v>26</v>
       </c>
       <c r="L27" t="s">
-        <v>234</v>
+        <v>211</v>
       </c>
       <c r="M27" t="s">
         <v>28</v>
       </c>
       <c r="N27" t="s">
-        <v>235</v>
+        <v>212</v>
       </c>
       <c r="O27" t="s">
-        <v>236</v>
+        <v>213</v>
       </c>
       <c r="P27" t="s">
-        <v>237</v>
+        <v>214</v>
       </c>
       <c r="Q27" t="s">
         <v>32</v>
@@ -2714,10 +2735,10 @@
         <v>1</v>
       </c>
       <c r="S27" t="s">
-        <v>77</v>
+        <v>44</v>
       </c>
       <c r="T27" t="s">
-        <v>238</v>
+        <v>215</v>
       </c>
       <c r="U27" t="s">
         <v>35</v>
@@ -2726,7 +2747,7 @@
         <v>36</v>
       </c>
       <c r="W27" t="s">
-        <v>239</v>
+        <v>216</v>
       </c>
     </row>
     <row r="28" spans="1:23" x14ac:dyDescent="0.3">
@@ -2734,10 +2755,10 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>240</v>
+        <v>217</v>
       </c>
       <c r="C28" t="s">
-        <v>241</v>
+        <v>170</v>
       </c>
       <c r="D28" t="s">
         <v>25</v>
@@ -2749,19 +2770,19 @@
         <v>26</v>
       </c>
       <c r="L28" t="s">
-        <v>242</v>
+        <v>218</v>
       </c>
       <c r="M28" t="s">
         <v>28</v>
       </c>
       <c r="N28" t="s">
-        <v>243</v>
+        <v>219</v>
       </c>
       <c r="O28" t="s">
-        <v>244</v>
+        <v>220</v>
       </c>
       <c r="P28" t="s">
-        <v>245</v>
+        <v>221</v>
       </c>
       <c r="Q28" t="s">
         <v>32</v>
@@ -2770,10 +2791,10 @@
         <v>1</v>
       </c>
       <c r="S28" t="s">
-        <v>246</v>
+        <v>69</v>
       </c>
       <c r="T28" t="s">
-        <v>247</v>
+        <v>222</v>
       </c>
       <c r="U28" t="s">
         <v>35</v>
@@ -2782,7 +2803,7 @@
         <v>36</v>
       </c>
       <c r="W28" t="s">
-        <v>248</v>
+        <v>223</v>
       </c>
     </row>
     <row r="29" spans="1:23" x14ac:dyDescent="0.3">
@@ -2790,10 +2811,10 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>249</v>
+        <v>224</v>
       </c>
       <c r="C29" t="s">
-        <v>250</v>
+        <v>225</v>
       </c>
       <c r="D29" t="s">
         <v>25</v>
@@ -2805,28 +2826,31 @@
         <v>26</v>
       </c>
       <c r="L29" t="s">
-        <v>251</v>
+        <v>226</v>
       </c>
       <c r="M29" t="s">
         <v>28</v>
       </c>
       <c r="N29" t="s">
-        <v>252</v>
+        <v>227</v>
       </c>
       <c r="O29" t="s">
-        <v>253</v>
+        <v>228</v>
       </c>
       <c r="P29" t="s">
-        <v>254</v>
+        <v>229</v>
       </c>
       <c r="Q29" t="s">
         <v>32</v>
       </c>
       <c r="R29" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="S29" t="s">
+        <v>271</v>
       </c>
       <c r="T29" t="s">
-        <v>255</v>
+        <v>230</v>
       </c>
       <c r="U29" t="s">
         <v>35</v>
@@ -2835,7 +2859,7 @@
         <v>36</v>
       </c>
       <c r="W29" t="s">
-        <v>256</v>
+        <v>231</v>
       </c>
     </row>
     <row r="30" spans="1:23" x14ac:dyDescent="0.3">
@@ -2843,10 +2867,10 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>257</v>
+        <v>232</v>
       </c>
       <c r="C30" t="s">
-        <v>258</v>
+        <v>233</v>
       </c>
       <c r="D30" t="s">
         <v>25</v>
@@ -2858,31 +2882,28 @@
         <v>26</v>
       </c>
       <c r="L30" t="s">
-        <v>259</v>
+        <v>234</v>
       </c>
       <c r="M30" t="s">
         <v>28</v>
       </c>
       <c r="N30" t="s">
-        <v>260</v>
+        <v>235</v>
       </c>
       <c r="O30" t="s">
-        <v>261</v>
+        <v>236</v>
       </c>
       <c r="P30" t="s">
-        <v>262</v>
+        <v>237</v>
       </c>
       <c r="Q30" t="s">
         <v>32</v>
       </c>
       <c r="R30" t="b">
-        <v>1</v>
-      </c>
-      <c r="S30" t="s">
-        <v>174</v>
+        <v>0</v>
       </c>
       <c r="T30" t="s">
-        <v>263</v>
+        <v>238</v>
       </c>
       <c r="U30" t="s">
         <v>35</v>
@@ -2891,7 +2912,63 @@
         <v>36</v>
       </c>
       <c r="W30" t="s">
-        <v>264</v>
+        <v>239</v>
+      </c>
+    </row>
+    <row r="31" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>240</v>
+      </c>
+      <c r="C31" t="s">
+        <v>241</v>
+      </c>
+      <c r="D31" t="s">
+        <v>25</v>
+      </c>
+      <c r="J31" t="s">
+        <v>26</v>
+      </c>
+      <c r="K31" t="s">
+        <v>26</v>
+      </c>
+      <c r="L31" t="s">
+        <v>242</v>
+      </c>
+      <c r="M31" t="s">
+        <v>28</v>
+      </c>
+      <c r="N31" t="s">
+        <v>243</v>
+      </c>
+      <c r="O31" t="s">
+        <v>244</v>
+      </c>
+      <c r="P31" t="s">
+        <v>245</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>32</v>
+      </c>
+      <c r="R31" t="b">
+        <v>1</v>
+      </c>
+      <c r="S31" t="s">
+        <v>158</v>
+      </c>
+      <c r="T31" t="s">
+        <v>246</v>
+      </c>
+      <c r="U31" t="s">
+        <v>35</v>
+      </c>
+      <c r="V31" t="s">
+        <v>36</v>
+      </c>
+      <c r="W31" t="s">
+        <v>247</v>
       </c>
     </row>
   </sheetData>
